--- a/data/trans_camb/P26-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P26-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,16; 8,03</t>
+          <t>0,07; 7,73</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,1; 4,05</t>
+          <t>-3,78; 4,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-14,35; -6,18</t>
+          <t>-14,55; -6,15</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 5,95</t>
+          <t>-1,92; 5,42</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-15,24; -7,37</t>
+          <t>-15,8; -7,97</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-24,71; -17,98</t>
+          <t>-24,82; -17,88</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,16; 5,65</t>
+          <t>0,07; 5,77</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-9,29; -3,45</t>
+          <t>-9,04; -3,19</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-18,99; -13,49</t>
+          <t>-19,11; -13,73</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,83; 39,54</t>
+          <t>0,29; 38,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-17,3; 19,99</t>
+          <t>-15,86; 21,5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-61,35; -29,46</t>
+          <t>-60,34; -29,01</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,97; 19,14</t>
+          <t>-5,8; 17,91</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-44,16; -24,4</t>
+          <t>-45,76; -25,33</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-71,55; -57,42</t>
+          <t>-71,86; -57,58</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,69; 21,52</t>
+          <t>0,26; 22,03</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-31,61; -13,34</t>
+          <t>-31,14; -11,93</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-65,53; -50,47</t>
+          <t>-65,84; -51,85</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,92; 7,48</t>
+          <t>0,18; 6,95</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,85; -2,71</t>
+          <t>-8,94; -2,53</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-22,21; 10,9</t>
+          <t>-22,33; 15,07</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 5,38</t>
+          <t>-1,62; 5,13</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-15,65; -8,86</t>
+          <t>-15,6; -8,84</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-33,37; -25,54</t>
+          <t>-33,52; -25,35</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,25; 5,2</t>
+          <t>0,14; 5,02</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-11,14; -6,5</t>
+          <t>-11,34; -6,66</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-25,72; -4,78</t>
+          <t>-25,58; -3,16</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,65; 23,96</t>
+          <t>0,5; 21,72</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-25,27; -8,17</t>
+          <t>-25,38; -8,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-65,94; 32,39</t>
+          <t>-65,9; 48,11</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 13,03</t>
+          <t>-3,73; 12,39</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-34,99; -21,42</t>
+          <t>-34,67; -21,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-76,69; -61,65</t>
+          <t>-77,22; -61,34</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,61; 14,25</t>
+          <t>0,35; 13,65</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-28,25; -17,85</t>
+          <t>-28,84; -18,11</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-67,11; -12,32</t>
+          <t>-66,75; -8,72</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 10,02</t>
+          <t>-2,42; 10,01</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-10,89; -0,37</t>
+          <t>-11,04; -0,57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-19,83; -10,39</t>
+          <t>-19,81; -9,84</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,18; 6,85</t>
+          <t>-6,65; 6,44</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-12,12; -0,31</t>
+          <t>-11,98; -0,11</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-22,57; -12,5</t>
+          <t>-22,91; -12,7</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 6,46</t>
+          <t>-2,27; 6,33</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-9,99; -2,23</t>
+          <t>-9,85; -2,12</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-19,84; -12,73</t>
+          <t>-19,7; -12,79</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-6,42; 44,19</t>
+          <t>-8,61; 42,55</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-38,57; -0,67</t>
+          <t>-38,41; -2,14</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-70,58; -45,19</t>
+          <t>-70,56; -43,16</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-19,39; 26,55</t>
+          <t>-20,05; 25,55</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-38,38; -1,3</t>
+          <t>-37,32; 0,36</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-69,66; -48,67</t>
+          <t>-71,16; -49,7</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-8,95; 25,38</t>
+          <t>-7,74; 25,37</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-34,68; -8,85</t>
+          <t>-34,03; -8,58</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-66,98; -50,24</t>
+          <t>-67,4; -50,0</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,14; 6,83</t>
+          <t>2,04; 6,81</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,91; -1,17</t>
+          <t>-5,51; -0,9</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-17,52; 10,54</t>
+          <t>-17,57; 8,04</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 4,12</t>
+          <t>-0,84; 4,24</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-12,62; -7,85</t>
+          <t>-12,68; -7,79</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-27,15; -21,94</t>
+          <t>-27,18; -21,94</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,32; 4,76</t>
+          <t>1,37; 4,86</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-8,31; -5,24</t>
+          <t>-8,42; -5,27</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-21,03; -5,3</t>
+          <t>-21,16; -7,29</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>7,08; 24,37</t>
+          <t>6,77; 24,94</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-19,95; -4,31</t>
+          <t>-18,5; -3,2</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-60,79; 37,3</t>
+          <t>-60,75; 27,42</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 11,48</t>
+          <t>-2,13; 11,97</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-33,05; -21,99</t>
+          <t>-33,11; -21,73</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-72,34; -60,62</t>
+          <t>-72,18; -60,92</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,95; 14,98</t>
+          <t>4,09; 15,17</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-24,78; -16,5</t>
+          <t>-25,07; -16,49</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-63,72; -16,33</t>
+          <t>-63,83; -22,39</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P26-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P26-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-10,37</t>
+          <t>-10,14</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-21,48</t>
+          <t>-21,79</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-16,48</t>
+          <t>-16,56</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,07; 7,73</t>
+          <t>-0,1; 7,9</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 4,32</t>
+          <t>-3,96; 4,34</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-14,55; -6,15</t>
+          <t>-14,16; -6,03</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 5,42</t>
+          <t>-2,44; 5,48</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-15,8; -7,97</t>
+          <t>-15,36; -7,5</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-24,82; -17,88</t>
+          <t>-25,16; -18,41</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,07; 5,77</t>
+          <t>0,23; 5,61</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-9,04; -3,19</t>
+          <t>-8,91; -3,33</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-19,11; -13,73</t>
+          <t>-18,88; -13,75</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-47,03%</t>
+          <t>-45,98%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-65,54%</t>
+          <t>-66,49%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-58,99%</t>
+          <t>-59,29%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,29; 38,12</t>
+          <t>-0,48; 39,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-15,86; 21,5</t>
+          <t>-16,67; 21,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-60,34; -29,01</t>
+          <t>-59,44; -28,13</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,8; 17,91</t>
+          <t>-6,81; 17,89</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-45,76; -25,33</t>
+          <t>-45,18; -24,32</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-71,86; -57,58</t>
+          <t>-72,24; -58,78</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,26; 22,03</t>
+          <t>0,75; 21,07</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-31,14; -11,93</t>
+          <t>-31,15; -12,58</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-65,84; -51,85</t>
+          <t>-65,37; -51,71</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-11,18</t>
+          <t>-21,59</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-28,89</t>
+          <t>-27,18</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-19,91</t>
+          <t>-24,26</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,18; 6,95</t>
+          <t>0,28; 6,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,94; -2,53</t>
+          <t>-9,26; -2,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-22,33; 15,07</t>
+          <t>-24,77; -18,87</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 5,13</t>
+          <t>-2,0; 5,53</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-15,6; -8,84</t>
+          <t>-15,44; -8,78</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-33,52; -25,35</t>
+          <t>-30,22; -24,37</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,14; 5,02</t>
+          <t>0,09; 4,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-11,34; -6,66</t>
+          <t>-11,09; -6,51</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-25,58; -3,16</t>
+          <t>-26,45; -22,26</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-33,51%</t>
+          <t>-64,69%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-67,68%</t>
+          <t>-63,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-52,52%</t>
+          <t>-64,0%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,5; 21,72</t>
+          <t>0,83; 21,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-25,38; -8,05</t>
+          <t>-25,93; -9,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-65,9; 48,11</t>
+          <t>-70,34; -58,49</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 12,39</t>
+          <t>-4,59; 13,45</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-34,67; -21,22</t>
+          <t>-34,79; -21,49</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-77,22; -61,34</t>
+          <t>-67,69; -58,97</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,35; 13,65</t>
+          <t>0,19; 13,67</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-28,84; -18,11</t>
+          <t>-28,27; -17,94</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-66,75; -8,72</t>
+          <t>-67,57; -60,72</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-15,22</t>
+          <t>-15,64</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-17,6</t>
+          <t>-17,86</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-16,28</t>
+          <t>-16,62</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 10,01</t>
+          <t>-2,58; 9,93</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-11,04; -0,57</t>
+          <t>-11,0; -0,15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-19,81; -9,84</t>
+          <t>-20,49; -11,04</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,65; 6,44</t>
+          <t>-6,14; 6,71</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-11,98; -0,11</t>
+          <t>-11,89; 0,01</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-22,91; -12,7</t>
+          <t>-22,79; -12,98</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 6,33</t>
+          <t>-2,13; 6,53</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-9,85; -2,12</t>
+          <t>-9,76; -1,93</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-19,7; -12,79</t>
+          <t>-20,41; -13,33</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-58,96%</t>
+          <t>-60,58%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-60,96%</t>
+          <t>-61,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-59,82%</t>
+          <t>-61,04%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-8,61; 42,55</t>
+          <t>-8,57; 44,26</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-38,41; -2,14</t>
+          <t>-39,18; -0,59</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-70,56; -43,16</t>
+          <t>-71,21; -47,28</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-20,05; 25,55</t>
+          <t>-19,45; 26,84</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-37,32; 0,36</t>
+          <t>-38,28; -0,27</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-71,16; -49,7</t>
+          <t>-70,21; -51,03</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-7,74; 25,37</t>
+          <t>-7,3; 26,51</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-34,03; -8,58</t>
+          <t>-33,4; -8,17</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-67,4; -50,0</t>
+          <t>-68,29; -52,56</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-10,12</t>
+          <t>-17,17</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-24,22</t>
+          <t>-23,39</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-17,28</t>
+          <t>-20,27</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,04; 6,81</t>
+          <t>1,74; 6,62</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,51; -0,9</t>
+          <t>-5,76; -1,19</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-17,57; 8,04</t>
+          <t>-19,34; -14,94</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 4,24</t>
+          <t>-0,9; 4,08</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-12,68; -7,79</t>
+          <t>-12,75; -7,98</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-27,18; -21,94</t>
+          <t>-25,64; -21,34</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,37; 4,86</t>
+          <t>1,34; 4,64</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-8,42; -5,27</t>
+          <t>-8,42; -5,18</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-21,16; -7,29</t>
+          <t>-21,58; -18,67</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-35,34%</t>
+          <t>-59,95%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-65,3%</t>
+          <t>-63,07%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-52,54%</t>
+          <t>-61,63%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>6,77; 24,94</t>
+          <t>5,39; 23,85</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-18,5; -3,2</t>
+          <t>-19,19; -4,2</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-60,75; 27,42</t>
+          <t>-65,27; -54,53</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 11,97</t>
+          <t>-2,59; 11,29</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-33,11; -21,73</t>
+          <t>-32,94; -22,15</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-72,18; -60,92</t>
+          <t>-66,47; -59,39</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,09; 15,17</t>
+          <t>4,04; 14,69</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-25,07; -16,49</t>
+          <t>-25,07; -16,29</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-63,83; -22,39</t>
+          <t>-64,5; -58,49</t>
         </is>
       </c>
     </row>
